--- a/TS Jatai Ghanam Project/Stas table for TS 1.1 TO 1.8.xlsx
+++ b/TS Jatai Ghanam Project/Stas table for TS 1.1 TO 1.8.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\texts\TS Jatai Ghanam Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\texts\TS Jatai Ghanam Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA83317-1B21-4920-A5E0-37F0C19A88E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7095" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TS 1.1" sheetId="8" r:id="rId1"/>
@@ -22,10 +23,19 @@
     <sheet name="TS 1.8" sheetId="6" r:id="rId8"/>
     <sheet name="total 1 to 8" sheetId="7" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2313,7 +2323,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2735,7 +2745,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2765,11 +2775,11 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3050,7 +3060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4318,19 +4328,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>355</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48"/>
@@ -5823,7 +5833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6103,8 +6113,8 @@
       <c r="K7" s="4">
         <v>50</v>
       </c>
-      <c r="L7" s="4">
-        <v>60</v>
+      <c r="L7" s="56">
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -7103,7 +7113,7 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="0"/>
-        <v>1797</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -7189,7 +7199,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9450,7 +9460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11599,7 +11609,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11673,7 +11683,7 @@
       <c r="F2" s="11">
         <v>3</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="11">
         <v>1</v>
       </c>
       <c r="H2" s="11">
@@ -11711,7 +11721,7 @@
       <c r="F3" s="11">
         <v>0</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="11">
         <v>1</v>
       </c>
       <c r="H3" s="11">
@@ -11749,7 +11759,7 @@
       <c r="F4" s="11">
         <v>1</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="11">
         <v>0</v>
       </c>
       <c r="H4" s="11">
@@ -11787,7 +11797,7 @@
       <c r="F5" s="11">
         <v>2</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="11">
         <v>0</v>
       </c>
       <c r="H5" s="11">
@@ -11825,7 +11835,7 @@
       <c r="F6" s="11">
         <v>3</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="11">
         <v>3</v>
       </c>
       <c r="H6" s="11">
@@ -11863,7 +11873,7 @@
       <c r="F7" s="11">
         <v>0</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="11">
         <v>1</v>
       </c>
       <c r="H7" s="11">
@@ -11901,7 +11911,7 @@
       <c r="F8" s="11">
         <v>1</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="11">
         <v>0</v>
       </c>
       <c r="H8" s="11">
@@ -11939,7 +11949,7 @@
       <c r="F9" s="11">
         <v>0</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="11">
         <v>7</v>
       </c>
       <c r="H9" s="11">
@@ -11977,7 +11987,7 @@
       <c r="F10" s="11">
         <v>0</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="11">
         <v>1</v>
       </c>
       <c r="H10" s="11">
@@ -12015,7 +12025,7 @@
       <c r="F11" s="11">
         <v>3</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="11">
         <v>2</v>
       </c>
       <c r="H11" s="11">
@@ -12053,7 +12063,7 @@
       <c r="F12" s="11">
         <v>0</v>
       </c>
-      <c r="G12" s="55">
+      <c r="G12" s="11">
         <v>10</v>
       </c>
       <c r="H12" s="11">
@@ -12091,7 +12101,7 @@
       <c r="F13" s="11">
         <v>4</v>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="11">
         <v>9</v>
       </c>
       <c r="H13" s="11">
@@ -12129,7 +12139,7 @@
       <c r="F14" s="11">
         <v>2</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="11">
         <v>4</v>
       </c>
       <c r="H14" s="11">
@@ -12167,7 +12177,7 @@
       <c r="F15" s="11">
         <v>1</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="11">
         <v>1</v>
       </c>
       <c r="H15" s="11">
@@ -12205,7 +12215,7 @@
       <c r="F16" s="11">
         <v>2</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="11">
         <v>2</v>
       </c>
       <c r="H16" s="11">
@@ -12243,7 +12253,7 @@
       <c r="F17" s="11">
         <v>1</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="11">
         <v>8</v>
       </c>
       <c r="H17" s="11">
@@ -12281,7 +12291,7 @@
       <c r="F18" s="11">
         <v>1</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="11">
         <v>2</v>
       </c>
       <c r="H18" s="11">
@@ -12319,7 +12329,7 @@
       <c r="F19" s="11">
         <v>3</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="11">
         <v>6</v>
       </c>
       <c r="H19" s="11">
@@ -12357,7 +12367,7 @@
       <c r="F20" s="11">
         <v>1</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="11">
         <v>4</v>
       </c>
       <c r="H20" s="11">
@@ -12395,7 +12405,7 @@
       <c r="F21" s="11">
         <v>4</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="11">
         <v>1</v>
       </c>
       <c r="H21" s="11">
@@ -12433,7 +12443,7 @@
       <c r="F22" s="11">
         <v>0</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="11">
         <v>1</v>
       </c>
       <c r="H22" s="11">
@@ -12471,7 +12481,7 @@
       <c r="F23" s="11">
         <v>0</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="11">
         <v>2</v>
       </c>
       <c r="H23" s="11">
@@ -12509,7 +12519,7 @@
       <c r="F24" s="11">
         <v>0</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="11">
         <v>2</v>
       </c>
       <c r="H24" s="11">
@@ -12547,7 +12557,7 @@
       <c r="F25" s="11">
         <v>1</v>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="11">
         <v>2</v>
       </c>
       <c r="H25" s="11">
@@ -12585,7 +12595,7 @@
       <c r="F26" s="11">
         <v>0</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="11">
         <v>5</v>
       </c>
       <c r="H26" s="11">
@@ -12623,7 +12633,7 @@
       <c r="F27" s="11">
         <v>0</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="11">
         <v>4</v>
       </c>
       <c r="H27" s="11">
@@ -12661,7 +12671,7 @@
       <c r="F28" s="11">
         <v>0</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="11">
         <v>1</v>
       </c>
       <c r="H28" s="11">
@@ -12699,7 +12709,7 @@
       <c r="F29" s="11">
         <v>1</v>
       </c>
-      <c r="G29" s="55">
+      <c r="G29" s="11">
         <v>0</v>
       </c>
       <c r="H29" s="11">
@@ -12737,7 +12747,7 @@
       <c r="F30" s="11">
         <v>0</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="11">
         <v>2</v>
       </c>
       <c r="H30" s="11">
@@ -12775,7 +12785,7 @@
       <c r="F31" s="11">
         <v>0</v>
       </c>
-      <c r="G31" s="55">
+      <c r="G31" s="11">
         <v>2</v>
       </c>
       <c r="H31" s="11">
@@ -12813,7 +12823,7 @@
       <c r="F32" s="11">
         <v>0</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="11">
         <v>5</v>
       </c>
       <c r="H32" s="11">
@@ -12851,7 +12861,7 @@
       <c r="F33" s="11">
         <v>1</v>
       </c>
-      <c r="G33" s="55">
+      <c r="G33" s="11">
         <v>3</v>
       </c>
       <c r="H33" s="11">
@@ -12889,7 +12899,7 @@
       <c r="F34" s="11">
         <v>0</v>
       </c>
-      <c r="G34" s="55">
+      <c r="G34" s="11">
         <v>1</v>
       </c>
       <c r="H34" s="11">
@@ -12927,7 +12937,7 @@
       <c r="F35" s="11">
         <v>0</v>
       </c>
-      <c r="G35" s="55">
+      <c r="G35" s="11">
         <v>3</v>
       </c>
       <c r="H35" s="11">
@@ -12965,7 +12975,7 @@
       <c r="F36" s="11">
         <v>0</v>
       </c>
-      <c r="G36" s="55">
+      <c r="G36" s="11">
         <v>5</v>
       </c>
       <c r="H36" s="11">
@@ -13003,7 +13013,7 @@
       <c r="F37" s="11">
         <v>0</v>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="11">
         <v>0</v>
       </c>
       <c r="H37" s="11">
@@ -13041,7 +13051,7 @@
       <c r="F38" s="11">
         <v>0</v>
       </c>
-      <c r="G38" s="55">
+      <c r="G38" s="11">
         <v>1</v>
       </c>
       <c r="H38" s="11">
@@ -13079,7 +13089,7 @@
       <c r="F39" s="11">
         <v>1</v>
       </c>
-      <c r="G39" s="55">
+      <c r="G39" s="11">
         <v>2</v>
       </c>
       <c r="H39" s="11">
@@ -13117,7 +13127,7 @@
       <c r="F40" s="11">
         <v>0</v>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="11">
         <v>3</v>
       </c>
       <c r="H40" s="11">
@@ -13155,7 +13165,7 @@
       <c r="F41" s="11">
         <v>0</v>
       </c>
-      <c r="G41" s="55">
+      <c r="G41" s="11">
         <v>3</v>
       </c>
       <c r="H41" s="11">
@@ -13193,7 +13203,7 @@
       <c r="F42" s="11">
         <v>0</v>
       </c>
-      <c r="G42" s="55">
+      <c r="G42" s="11">
         <v>4</v>
       </c>
       <c r="H42" s="11">
@@ -13231,7 +13241,7 @@
       <c r="F43" s="11">
         <v>0</v>
       </c>
-      <c r="G43" s="55">
+      <c r="G43" s="11">
         <v>5</v>
       </c>
       <c r="H43" s="11">
@@ -13269,7 +13279,7 @@
       <c r="F44" s="11">
         <v>0</v>
       </c>
-      <c r="G44" s="55">
+      <c r="G44" s="11">
         <v>0</v>
       </c>
       <c r="H44" s="11">
@@ -13307,7 +13317,7 @@
       <c r="F45" s="11">
         <v>0</v>
       </c>
-      <c r="G45" s="55">
+      <c r="G45" s="11">
         <v>0</v>
       </c>
       <c r="H45" s="11">
@@ -13345,7 +13355,7 @@
       <c r="F46" s="11">
         <v>1</v>
       </c>
-      <c r="G46" s="55">
+      <c r="G46" s="11">
         <v>1</v>
       </c>
       <c r="H46" s="11">
@@ -13383,7 +13393,7 @@
       <c r="F47" s="11">
         <v>7</v>
       </c>
-      <c r="G47" s="55">
+      <c r="G47" s="11">
         <v>6</v>
       </c>
       <c r="H47" s="11">
@@ -13421,7 +13431,7 @@
       <c r="F48" s="11">
         <v>7</v>
       </c>
-      <c r="G48" s="55">
+      <c r="G48" s="11">
         <v>4</v>
       </c>
       <c r="H48" s="11">
@@ -13459,7 +13469,7 @@
       <c r="F49" s="11">
         <v>6</v>
       </c>
-      <c r="G49" s="55">
+      <c r="G49" s="11">
         <v>4</v>
       </c>
       <c r="H49" s="11">
@@ -13497,7 +13507,7 @@
       <c r="F50" s="11">
         <v>6</v>
       </c>
-      <c r="G50" s="55">
+      <c r="G50" s="11">
         <v>3</v>
       </c>
       <c r="H50" s="11">
@@ -13535,7 +13545,7 @@
       <c r="F51" s="11">
         <v>6</v>
       </c>
-      <c r="G51" s="55">
+      <c r="G51" s="11">
         <v>7</v>
       </c>
       <c r="H51" s="11">
@@ -13573,7 +13583,7 @@
       <c r="F52" s="11">
         <v>6</v>
       </c>
-      <c r="G52" s="55">
+      <c r="G52" s="11">
         <v>0</v>
       </c>
       <c r="H52" s="11">
@@ -13758,7 +13768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13832,7 +13842,7 @@
       <c r="F2" s="11">
         <v>0</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="11">
         <v>6</v>
       </c>
       <c r="H2" s="11">
@@ -13870,7 +13880,7 @@
       <c r="F3" s="11">
         <v>0</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="11">
         <v>1</v>
       </c>
       <c r="H3" s="11">
@@ -13908,7 +13918,7 @@
       <c r="F4" s="11">
         <v>0</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="11">
         <v>2</v>
       </c>
       <c r="H4" s="11">
@@ -13946,7 +13956,7 @@
       <c r="F5" s="11">
         <v>0</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="11">
         <v>3</v>
       </c>
       <c r="H5" s="11">
@@ -13984,7 +13994,7 @@
       <c r="F6" s="11">
         <v>0</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="11">
         <v>6</v>
       </c>
       <c r="H6" s="11">
@@ -14022,7 +14032,7 @@
       <c r="F7" s="11">
         <v>1</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="11">
         <v>5</v>
       </c>
       <c r="H7" s="11">
@@ -14060,7 +14070,7 @@
       <c r="F8" s="11">
         <v>0</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="11">
         <v>3</v>
       </c>
       <c r="H8" s="11">
@@ -14098,7 +14108,7 @@
       <c r="F9" s="11">
         <v>0</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="11">
         <v>3</v>
       </c>
       <c r="H9" s="11">
@@ -14136,7 +14146,7 @@
       <c r="F10" s="11">
         <v>0</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="11">
         <v>6</v>
       </c>
       <c r="H10" s="11">
@@ -14174,7 +14184,7 @@
       <c r="F11" s="11">
         <v>1</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="11">
         <v>7</v>
       </c>
       <c r="H11" s="11">
@@ -14212,7 +14222,7 @@
       <c r="F12" s="11">
         <v>0</v>
       </c>
-      <c r="G12" s="55">
+      <c r="G12" s="11">
         <v>1</v>
       </c>
       <c r="H12" s="11">
@@ -14250,7 +14260,7 @@
       <c r="F13" s="11">
         <v>0</v>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="11">
         <v>0</v>
       </c>
       <c r="H13" s="11">
@@ -14288,7 +14298,7 @@
       <c r="F14" s="11">
         <v>0</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="11">
         <v>2</v>
       </c>
       <c r="H14" s="11">
@@ -14326,7 +14336,7 @@
       <c r="F15" s="11">
         <v>1</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="11">
         <v>2</v>
       </c>
       <c r="H15" s="11">
@@ -14364,7 +14374,7 @@
       <c r="F16" s="11">
         <v>0</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="11">
         <v>1</v>
       </c>
       <c r="H16" s="11">
@@ -14402,7 +14412,7 @@
       <c r="F17" s="11">
         <v>0</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="11">
         <v>10</v>
       </c>
       <c r="H17" s="11">
@@ -14440,7 +14450,7 @@
       <c r="F18" s="11">
         <v>0</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="11">
         <v>1</v>
       </c>
       <c r="H18" s="11">
@@ -14478,7 +14488,7 @@
       <c r="F19" s="11">
         <v>0</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="11">
         <v>4</v>
       </c>
       <c r="H19" s="11">
@@ -14516,7 +14526,7 @@
       <c r="F20" s="11">
         <v>0</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="11">
         <v>1</v>
       </c>
       <c r="H20" s="11">
@@ -14554,7 +14564,7 @@
       <c r="F21" s="11">
         <v>1</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="11">
         <v>4</v>
       </c>
       <c r="H21" s="11">
@@ -14592,7 +14602,7 @@
       <c r="F22" s="11">
         <v>0</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="11">
         <v>7</v>
       </c>
       <c r="H22" s="11">
@@ -14630,7 +14640,7 @@
       <c r="F23" s="11">
         <v>0</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="11">
         <v>1</v>
       </c>
       <c r="H23" s="11">
@@ -14668,7 +14678,7 @@
       <c r="F24" s="11">
         <v>0</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="11">
         <v>2</v>
       </c>
       <c r="H24" s="11">
@@ -14706,7 +14716,7 @@
       <c r="F25" s="11">
         <v>1</v>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="11">
         <v>4</v>
       </c>
       <c r="H25" s="11">
@@ -14744,7 +14754,7 @@
       <c r="F26" s="11">
         <v>0</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="11">
         <v>3</v>
       </c>
       <c r="H26" s="11">
@@ -14782,7 +14792,7 @@
       <c r="F27" s="11">
         <v>0</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="11">
         <v>1</v>
       </c>
       <c r="H27" s="11">
@@ -14820,7 +14830,7 @@
       <c r="F28" s="11">
         <v>0</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="11">
         <v>6</v>
       </c>
       <c r="H28" s="11">
@@ -14858,7 +14868,7 @@
       <c r="F29" s="11">
         <v>0</v>
       </c>
-      <c r="G29" s="55">
+      <c r="G29" s="11">
         <v>3</v>
       </c>
       <c r="H29" s="11">
@@ -14896,7 +14906,7 @@
       <c r="F30" s="11">
         <v>0</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="11">
         <v>2</v>
       </c>
       <c r="H30" s="11">
@@ -14934,7 +14944,7 @@
       <c r="F31" s="11">
         <v>0</v>
       </c>
-      <c r="G31" s="55">
+      <c r="G31" s="11">
         <v>2</v>
       </c>
       <c r="H31" s="11">
@@ -14972,7 +14982,7 @@
       <c r="F32" s="11">
         <v>1</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="11">
         <v>9</v>
       </c>
       <c r="H32" s="11">
@@ -15010,7 +15020,7 @@
       <c r="F33" s="11">
         <v>5</v>
       </c>
-      <c r="G33" s="55">
+      <c r="G33" s="11">
         <v>2</v>
       </c>
       <c r="H33" s="11">
@@ -15048,7 +15058,7 @@
       <c r="F34" s="11">
         <v>5</v>
       </c>
-      <c r="G34" s="55">
+      <c r="G34" s="11">
         <v>2</v>
       </c>
       <c r="H34" s="11">
@@ -15086,7 +15096,7 @@
       <c r="F35" s="11">
         <v>2</v>
       </c>
-      <c r="G35" s="55">
+      <c r="G35" s="11">
         <v>1</v>
       </c>
       <c r="H35" s="11">
@@ -15124,7 +15134,7 @@
       <c r="F36" s="11">
         <v>6</v>
       </c>
-      <c r="G36" s="55">
+      <c r="G36" s="11">
         <v>0</v>
       </c>
       <c r="H36" s="11">
@@ -15162,7 +15172,7 @@
       <c r="F37" s="11">
         <v>6</v>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="11">
         <v>7</v>
       </c>
       <c r="H37" s="11">
@@ -15200,7 +15210,7 @@
       <c r="F38" s="11">
         <v>2</v>
       </c>
-      <c r="G38" s="55">
+      <c r="G38" s="11">
         <v>4</v>
       </c>
       <c r="H38" s="11">
@@ -15238,7 +15248,7 @@
       <c r="F39" s="11">
         <v>1</v>
       </c>
-      <c r="G39" s="55">
+      <c r="G39" s="11">
         <v>1</v>
       </c>
       <c r="H39" s="11">
@@ -15276,7 +15286,7 @@
       <c r="F40" s="11">
         <v>1</v>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="11">
         <v>4</v>
       </c>
       <c r="H40" s="11">
@@ -15314,7 +15324,7 @@
       <c r="F41" s="11">
         <v>5</v>
       </c>
-      <c r="G41" s="55">
+      <c r="G41" s="11">
         <v>2</v>
       </c>
       <c r="H41" s="11">
@@ -15352,7 +15362,7 @@
       <c r="F42" s="11">
         <v>6</v>
       </c>
-      <c r="G42" s="55">
+      <c r="G42" s="11">
         <v>9</v>
       </c>
       <c r="H42" s="11">
@@ -15390,7 +15400,7 @@
       <c r="F43" s="11">
         <v>4</v>
       </c>
-      <c r="G43" s="55">
+      <c r="G43" s="11">
         <v>2</v>
       </c>
       <c r="H43" s="11">
@@ -15428,7 +15438,7 @@
       <c r="F44" s="11">
         <v>0</v>
       </c>
-      <c r="G44" s="55">
+      <c r="G44" s="11">
         <v>9</v>
       </c>
       <c r="H44" s="11">
@@ -15466,7 +15476,7 @@
       <c r="F45" s="11">
         <v>1</v>
       </c>
-      <c r="G45" s="55">
+      <c r="G45" s="11">
         <v>8</v>
       </c>
       <c r="H45" s="11">
@@ -15504,7 +15514,7 @@
       <c r="F46" s="11">
         <v>2</v>
       </c>
-      <c r="G46" s="55">
+      <c r="G46" s="11">
         <v>0</v>
       </c>
       <c r="H46" s="11">
@@ -15542,7 +15552,7 @@
       <c r="F47" s="11">
         <v>7</v>
       </c>
-      <c r="G47" s="55">
+      <c r="G47" s="11">
         <v>3</v>
       </c>
       <c r="H47" s="11">
@@ -15580,7 +15590,7 @@
       <c r="F48" s="11">
         <v>5</v>
       </c>
-      <c r="G48" s="55">
+      <c r="G48" s="11">
         <v>11</v>
       </c>
       <c r="H48" s="11">
@@ -15618,7 +15628,7 @@
       <c r="F49" s="11">
         <v>6</v>
       </c>
-      <c r="G49" s="55">
+      <c r="G49" s="11">
         <v>1</v>
       </c>
       <c r="H49" s="11">
@@ -15656,7 +15666,7 @@
       <c r="F50" s="11">
         <v>4</v>
       </c>
-      <c r="G50" s="55">
+      <c r="G50" s="11">
         <v>6</v>
       </c>
       <c r="H50" s="11">
@@ -15694,7 +15704,7 @@
       <c r="F51" s="11">
         <v>6</v>
       </c>
-      <c r="G51" s="55">
+      <c r="G51" s="11">
         <v>6</v>
       </c>
       <c r="H51" s="11">
@@ -15732,7 +15742,7 @@
       <c r="F52" s="11">
         <v>9</v>
       </c>
-      <c r="G52" s="55">
+      <c r="G52" s="11">
         <v>3</v>
       </c>
       <c r="H52" s="11">
@@ -15906,7 +15916,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15977,10 +15987,10 @@
       <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="55">
-        <v>0</v>
-      </c>
-      <c r="G2" s="55">
+      <c r="F2" s="11">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
         <v>3</v>
       </c>
       <c r="H2" s="11">
@@ -16015,10 +16025,10 @@
       <c r="E3" s="11">
         <v>0</v>
       </c>
-      <c r="F3" s="55">
-        <v>1</v>
-      </c>
-      <c r="G3" s="55">
+      <c r="F3" s="11">
+        <v>1</v>
+      </c>
+      <c r="G3" s="11">
         <v>0</v>
       </c>
       <c r="H3" s="11">
@@ -16053,10 +16063,10 @@
       <c r="E4" s="11">
         <v>0</v>
       </c>
-      <c r="F4" s="55">
-        <v>1</v>
-      </c>
-      <c r="G4" s="55">
+      <c r="F4" s="11">
+        <v>1</v>
+      </c>
+      <c r="G4" s="11">
         <v>1</v>
       </c>
       <c r="H4" s="11">
@@ -16091,10 +16101,10 @@
       <c r="E5" s="11">
         <v>0</v>
       </c>
-      <c r="F5" s="55">
+      <c r="F5" s="11">
         <v>9</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="11">
         <v>3</v>
       </c>
       <c r="H5" s="11">
@@ -16129,10 +16139,10 @@
       <c r="E6" s="11">
         <v>1</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="11">
         <v>3</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="11">
         <v>7</v>
       </c>
       <c r="H6" s="11">
@@ -16167,10 +16177,10 @@
       <c r="E7" s="11">
         <v>0</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="11">
         <v>2</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="11">
         <v>3</v>
       </c>
       <c r="H7" s="11">
@@ -16208,7 +16218,7 @@
       <c r="F8" s="11">
         <v>3</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="11">
         <v>5</v>
       </c>
       <c r="H8" s="11">
@@ -16246,7 +16256,7 @@
       <c r="F9" s="11">
         <v>7</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="11">
         <v>5</v>
       </c>
       <c r="H9" s="11">
@@ -16284,7 +16294,7 @@
       <c r="F10" s="11">
         <v>6</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="11">
         <v>1</v>
       </c>
       <c r="H10" s="11">
@@ -16322,7 +16332,7 @@
       <c r="F11" s="11">
         <v>0</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="11">
         <v>1</v>
       </c>
       <c r="H11" s="11">
@@ -16360,7 +16370,7 @@
       <c r="F12" s="11">
         <v>6</v>
       </c>
-      <c r="G12" s="55">
+      <c r="G12" s="11">
         <v>3</v>
       </c>
       <c r="H12" s="11">
@@ -16398,7 +16408,7 @@
       <c r="F13" s="11">
         <v>0</v>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="11">
         <v>1</v>
       </c>
       <c r="H13" s="11">
@@ -16436,7 +16446,7 @@
       <c r="F14" s="11">
         <v>1</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="11">
         <v>2</v>
       </c>
       <c r="H14" s="11">
@@ -16474,7 +16484,7 @@
       <c r="F15" s="11">
         <v>1</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="11">
         <v>5</v>
       </c>
       <c r="H15" s="11">
@@ -16512,7 +16522,7 @@
       <c r="F16" s="11">
         <v>0</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="11">
         <v>1</v>
       </c>
       <c r="H16" s="11">
@@ -16550,7 +16560,7 @@
       <c r="F17" s="11">
         <v>0</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="11">
         <v>2</v>
       </c>
       <c r="H17" s="11">
@@ -16588,7 +16598,7 @@
       <c r="F18" s="11">
         <v>1</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="11">
         <v>1</v>
       </c>
       <c r="H18" s="11">
@@ -16626,7 +16636,7 @@
       <c r="F19" s="11">
         <v>0</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="11">
         <v>1</v>
       </c>
       <c r="H19" s="11">
@@ -16664,7 +16674,7 @@
       <c r="F20" s="11">
         <v>1</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="11">
         <v>3</v>
       </c>
       <c r="H20" s="11">
@@ -16702,7 +16712,7 @@
       <c r="F21" s="11">
         <v>3</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="11">
         <v>1</v>
       </c>
       <c r="H21" s="11">
@@ -16740,7 +16750,7 @@
       <c r="F22" s="11">
         <v>2</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="11">
         <v>2</v>
       </c>
       <c r="H22" s="11">
@@ -16778,7 +16788,7 @@
       <c r="F23" s="11">
         <v>1</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="11">
         <v>0</v>
       </c>
       <c r="H23" s="11">
@@ -16816,7 +16826,7 @@
       <c r="F24" s="11">
         <v>1</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="11">
         <v>1</v>
       </c>
       <c r="H24" s="11">
@@ -16854,7 +16864,7 @@
       <c r="F25" s="11">
         <v>0</v>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="11">
         <v>4</v>
       </c>
       <c r="H25" s="11">
@@ -16892,7 +16902,7 @@
       <c r="F26" s="11">
         <v>1</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="11">
         <v>1</v>
       </c>
       <c r="H26" s="11">
@@ -16930,7 +16940,7 @@
       <c r="F27" s="11">
         <v>2</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="11">
         <v>0</v>
       </c>
       <c r="H27" s="11">
@@ -16968,7 +16978,7 @@
       <c r="F28" s="11">
         <v>2</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="11">
         <v>1</v>
       </c>
       <c r="H28" s="11">
@@ -17006,7 +17016,7 @@
       <c r="F29" s="11">
         <v>4</v>
       </c>
-      <c r="G29" s="55">
+      <c r="G29" s="11">
         <v>3</v>
       </c>
       <c r="H29" s="11">
@@ -17044,7 +17054,7 @@
       <c r="F30" s="11">
         <v>0</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="11">
         <v>1</v>
       </c>
       <c r="H30" s="11">
@@ -17082,7 +17092,7 @@
       <c r="F31" s="11">
         <v>2</v>
       </c>
-      <c r="G31" s="55">
+      <c r="G31" s="11">
         <v>0</v>
       </c>
       <c r="H31" s="11">
@@ -17120,7 +17130,7 @@
       <c r="F32" s="11">
         <v>0</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="11">
         <v>5</v>
       </c>
       <c r="H32" s="11">
@@ -17158,7 +17168,7 @@
       <c r="F33" s="11">
         <v>2</v>
       </c>
-      <c r="G33" s="55">
+      <c r="G33" s="11">
         <v>1</v>
       </c>
       <c r="H33" s="11">
@@ -17196,7 +17206,7 @@
       <c r="F34" s="11">
         <v>1</v>
       </c>
-      <c r="G34" s="55">
+      <c r="G34" s="11">
         <v>1</v>
       </c>
       <c r="H34" s="11">
@@ -17234,7 +17244,7 @@
       <c r="F35" s="11">
         <v>1</v>
       </c>
-      <c r="G35" s="55">
+      <c r="G35" s="11">
         <v>1</v>
       </c>
       <c r="H35" s="11">
@@ -17272,7 +17282,7 @@
       <c r="F36" s="11">
         <v>1</v>
       </c>
-      <c r="G36" s="55">
+      <c r="G36" s="11">
         <v>3</v>
       </c>
       <c r="H36" s="11">
@@ -17310,7 +17320,7 @@
       <c r="F37" s="11">
         <v>1</v>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="11">
         <v>2</v>
       </c>
       <c r="H37" s="11">
@@ -17348,7 +17358,7 @@
       <c r="F38" s="11">
         <v>7</v>
       </c>
-      <c r="G38" s="55">
+      <c r="G38" s="11">
         <v>3</v>
       </c>
       <c r="H38" s="11">
@@ -17386,7 +17396,7 @@
       <c r="F39" s="11">
         <v>6</v>
       </c>
-      <c r="G39" s="55">
+      <c r="G39" s="11">
         <v>6</v>
       </c>
       <c r="H39" s="11">
@@ -17424,7 +17434,7 @@
       <c r="F40" s="11">
         <v>7</v>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="11">
         <v>2</v>
       </c>
       <c r="H40" s="11">
@@ -17462,7 +17472,7 @@
       <c r="F41" s="11">
         <v>7</v>
       </c>
-      <c r="G41" s="55">
+      <c r="G41" s="11">
         <v>4</v>
       </c>
       <c r="H41" s="11">
@@ -17500,7 +17510,7 @@
       <c r="F42" s="11">
         <v>6</v>
       </c>
-      <c r="G42" s="55">
+      <c r="G42" s="11">
         <v>3</v>
       </c>
       <c r="H42" s="11">
@@ -17538,7 +17548,7 @@
       <c r="F43" s="11">
         <v>9</v>
       </c>
-      <c r="G43" s="55">
+      <c r="G43" s="11">
         <v>4</v>
       </c>
       <c r="H43" s="11">
@@ -17718,7 +17728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17735,7 +17745,7 @@
     <col min="13" max="13" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
@@ -17767,7 +17777,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="94.5" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
         <v>300</v>
       </c>
